--- a/output/pdf_financials_xlsx/DTOL.xlsx
+++ b/output/pdf_financials_xlsx/DTOL.xlsx
@@ -699,22 +699,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>83.121</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>170.143</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>1335.965</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>4225.939</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>3765.5</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>2936.633</v>
       </c>
     </row>
     <row r="13">
@@ -1098,22 +1098,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-41306.165</v>
+        <v>-41389.286</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-97817.13099999999</v>
+        <v>-97987.274</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-17942.637</v>
+        <v>-19278.602</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-3.196</v>
+        <v>-4229.135</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>9486.548000000001</v>
+        <v>5721.048</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>13077.801</v>
+        <v>10141.168</v>
       </c>
     </row>
     <row r="28">
@@ -1148,22 +1148,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-41288.438</v>
+        <v>-41371.559</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-97393.735</v>
+        <v>-97563.878</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-17344.092</v>
+        <v>-18680.057</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>84.901</v>
+        <v>-4141.038</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>10772.082</v>
+        <v>7006.582</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>15338.139</v>
+        <v>12401.506</v>
       </c>
     </row>
     <row r="30">
@@ -1173,22 +1173,22 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-32.67208203372026</v>
+        <v>-32.73785677023911</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-64125.45101395839</v>
+        <v>-64237.4756386621</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-10299.58668851992</v>
+        <v>-11092.93391767025</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>46.55170523083672</v>
+        <v>-2270.554885404101</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>5.247602886260943</v>
+        <v>3.413245454873438</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>7.052950833758788</v>
+        <v>5.70259612868058</v>
       </c>
     </row>
     <row r="31">
@@ -11076,7 +11076,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E167" s="5" t="n">
@@ -11120,7 +11120,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E168" s="5" t="n">
@@ -13414,7 +13414,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -13458,7 +13458,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">

--- a/output/pdf_financials_xlsx/DTOL.xlsx
+++ b/output/pdf_financials_xlsx/DTOL.xlsx
@@ -1123,22 +1123,22 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>17.727</v>
+        <v>3135.883</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>423.396</v>
+        <v>3499.139</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>598.545</v>
+        <v>4243.532</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>88.09699999999999</v>
+        <v>2871.145</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>1285.534</v>
+        <v>4262.048</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>2260.338</v>
+        <v>5310.711</v>
       </c>
     </row>
     <row r="29">
@@ -1148,22 +1148,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-41371.559</v>
+        <v>-38253.403</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-97563.878</v>
+        <v>-94488.13499999999</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-18680.057</v>
+        <v>-15035.07</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-4141.038</v>
+        <v>-1357.99</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>7006.582</v>
+        <v>9983.096</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>12401.506</v>
+        <v>15451.879</v>
       </c>
     </row>
     <row r="30">
@@ -1173,22 +1173,22 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-32.73785677023911</v>
+        <v>-30.27041906707541</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-64237.4756386621</v>
+        <v>-62212.36173294707</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-11092.93391767025</v>
+        <v>-8928.400912135679</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-2270.554885404101</v>
+        <v>-744.593705450159</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>3.413245454873438</v>
+        <v>4.863249591250798</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>5.70259612868058</v>
+        <v>7.105252004574343</v>
       </c>
     </row>
     <row r="31">
@@ -2899,22 +2899,22 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>3135.883</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>3499.139</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>4243.532</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>2871.145</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>4262.048</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>5310.711</v>
       </c>
     </row>
     <row r="101">
@@ -3214,7 +3214,7 @@
         <v>0</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>24.67</v>
       </c>
     </row>
     <row r="113">
@@ -6278,7 +6278,11 @@
           <t>Depreciation of property and equipment (note 6)</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E57" s="5" t="n">
         <v>1248.324</v>
       </c>
@@ -6314,7 +6318,11 @@
           <t>Depreciation of right-of-use assets (note 9(a))</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E58" s="5" t="n">
         <v>1869.832</v>
       </c>
@@ -6356,7 +6364,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E59" s="5" t="n">
@@ -7464,7 +7472,11 @@
           <t>Proceeds from disposal of property and equipment (note 6)</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
@@ -8072,7 +8084,11 @@
           <t>Depreciation of right-of-use assets (note 9)</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
           <t>-</t>
